--- a/F3M_Fiscal_assessment_ready_AI_v0.xlsx
+++ b/F3M_Fiscal_assessment_ready_AI_v0.xlsx
@@ -131,10 +131,10 @@
     <t>Proceso integrado con cierre, reporting, consolidación y fiscalidad local, con controles automatizados, trazabilidad y mejora continua.</t>
   </si>
   <si>
-    <t>Tax accounting continuo y AI-enabled, con generación asistida de provisiones, validaciones inteligentes, alertas de desviación y explicación automática de variaciones.</t>
-  </si>
-  <si>
-    <t>Accurate tax report generation; Automated financial statement preparation; Generate account variance analysis and intelligent explanations</t>
+    <t>Tax accounting continuo y basado en IA, con generación asistida de provisiones, validaciones inteligentes, alertas de desviación y explicación automática de variaciones.</t>
+  </si>
+  <si>
+    <t>Generación precisa de informes fiscales; Preparación automatizada de estados financieros; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
   </si>
   <si>
     <t>¿Existe calendario formal de provisión fiscal?
@@ -170,7 +170,7 @@
     <t>Motor inteligente de cálculo fiscal con detección de inconsistencias, explicación de drivers de ETR y recomendaciones de revisión de diferidos o posiciones fiscales.</t>
   </si>
   <si>
-    <t>Accurate tax report generation; Identify inconsistencies in master data records; Generate account variance analysis and intelligent explanations</t>
+    <t>Generación precisa de informes fiscales; Identificación de inconsistencias en los registros de datos maestros; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
   </si>
   <si>
     <t>¿El cálculo de impuesto corriente/diferido es trazable?
@@ -203,10 +203,10 @@
     <t>Capa integrada de datos fiscal-contables con controles automáticos, reconciliaciones recurrentes, gestión de incidencias y trazabilidad end-to-end.</t>
   </si>
   <si>
-    <t>AI detecta inconsistencias, clasificaciones anómalas y gaps de dato, genera metadata fiscal y recomienda acciones de remediación.</t>
-  </si>
-  <si>
-    <t>Automate financial data across diverse sources; Identify inconsistencies in master data records; Generate metadata documentation</t>
+    <t>IA detecta inconsistencias, clasificaciones anómalas y gaps de dato, genera metadata fiscal y recomienda acciones de remediación.</t>
+  </si>
+  <si>
+    <t>Automatización de datos financieros de fuentes diversas; Identificación de inconsistencias en los registros de datos maestros; Generación de documentación de metadatos</t>
   </si>
   <si>
     <t>¿Existen fuentes oficiales para datos fiscales?
@@ -239,10 +239,10 @@
     <t>Reporting integrado con cierre, forecast, auditoría, riesgos fiscales, acciones y revisión ejecutiva periódica.</t>
   </si>
   <si>
-    <t>Reporting fiscal AI-enabled con generación automática de narrative commentary, explicación de variaciones, alertas y recomendaciones de gestión.</t>
-  </si>
-  <si>
-    <t>Accurate tax report generation; Consolidate written financial reports into one compliant report; Generate account variance analysis and intelligent explanations</t>
+    <t>Reporting fiscal basado en IA con generación automática de narrative commentary, explicación de variaciones, alertas y recomendaciones de gestión.</t>
+  </si>
+  <si>
+    <t>Generación precisa de informes fiscales; Consolidación de informes financieros en un único informe conforme a normativa; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
   </si>
   <si>
     <t>¿Se reporta ETR/cash tax/diferidos de forma ejecutiva?
@@ -278,10 +278,10 @@
     <t>Cumplimiento integrado con datos financieros, workflow, gestión documental, alertas y reporting de estatus/riesgos.</t>
   </si>
   <si>
-    <t>Compliance directo AI-enabled con monitorización de vencimientos, revisión asistida de obligaciones, alertas regulatorias y generación de borradores.</t>
-  </si>
-  <si>
-    <t>Automate tax filing processes, analyze financial data, and generate accurate tax reports; Automated regulatory compliance; Global policy tracking</t>
+    <t>Compliance directo basado en IA con monitorización de vencimientos, revisión asistida de obligaciones, alertas regulatorias y generación de borradores.</t>
+  </si>
+  <si>
+    <t>Automatización de la presentación de impuestos, análisis de datos financieros y generación precisa de informes fiscales; Cumplimiento regulatorio automatizado; Seguimiento de políticas globales</t>
   </si>
   <si>
     <t>¿Existe calendario fiscal de impuestos directos?
@@ -314,10 +314,10 @@
     <t>Preparación integrada con datos financieros oficiales, validaciones automáticas, workflow de revisión y trazabilidad de ajustes.</t>
   </si>
   <si>
-    <t>Generación asistida de declaraciones con AI/NLP, validaciones inteligentes, detección de inconsistencias y preparación de documentación soporte.</t>
-  </si>
-  <si>
-    <t>Automate tax filing processes, analyze financial data, and generate accurate tax reports; Accurate tax report generation; Financial rules and regulations interpretations</t>
+    <t>Generación asistida de declaraciones con IA/NLP, validaciones inteligentes, detección de inconsistencias y preparación de documentación soporte.</t>
+  </si>
+  <si>
+    <t>Automatización de la presentación de impuestos, análisis de datos financieros y generación precisa de informes fiscales; Generación precisa de informes fiscales; Interpretación de normas y regulación financiera</t>
   </si>
   <si>
     <t>¿Las declaraciones se preparan con proceso estándar?
@@ -350,10 +350,10 @@
     <t>Gestión integrada de controversias con workflow, repositorio documental, scoring de riesgo, reporting de exposición y aprendizaje recurrente.</t>
   </si>
   <si>
-    <t>AI sintetiza requerimientos, localiza evidencias, propone borradores de respuesta, identifica riesgos y prioriza controversias por exposición.</t>
-  </si>
-  <si>
-    <t>AI-powered archive access and extraction; Financial rules and regulations interpretations; Research-based report generation / KYC</t>
+    <t>IA sintetiza requerimientos, localiza evidencias, propone borradores de respuesta, identifica riesgos y prioriza controversias por exposición.</t>
+  </si>
+  <si>
+    <t>Acceso y extracción documental impulsados por IA; Interpretación de normas y regulación financiera; Generación de informes de investigación / KYC</t>
   </si>
   <si>
     <t>¿Existe tracker de requerimientos y controversias?
@@ -386,10 +386,10 @@
     <t>Modelo de mejora continua con análisis causa-raíz, controles preventivos, automatización progresiva y reporting de calidad del cumplimiento.</t>
   </si>
   <si>
-    <t>AI detecta patrones de error, anticipa riesgos de incumplimiento, recomienda controles preventivos y prioriza acciones de mejora.</t>
-  </si>
-  <si>
-    <t>Predictive compliance monitoring; Automated regulatory compliance; Proactive defect resolution recommendations</t>
+    <t>IA detecta patrones de error, anticipa riesgos de incumplimiento, recomienda controles preventivos y prioriza acciones de mejora.</t>
+  </si>
+  <si>
+    <t>Monitorización predictiva del cumplimiento; Cumplimiento regulatorio automatizado; Recomendaciones proactivas para la resolución de incidencias</t>
   </si>
   <si>
     <t>¿Se miden errores y retrasos?
@@ -425,10 +425,10 @@
     <t>Modelo integrado con procesos comerciales, compras, ERP, facturación, maestros fiscales, controles automáticos y reporting de incidencias.</t>
   </si>
   <si>
-    <t>Modelo indirect tax AI-enabled con monitorización continua de transacciones, detección de errores, alertas regulatorias y recomendaciones de tratamiento fiscal.</t>
-  </si>
-  <si>
-    <t>Automated regulatory compliance; Financial rules and regulations interpretations; Identify inconsistencies in master data records</t>
+    <t>Modelo indirect tax basado en IA con monitorización continua de transacciones, detección de errores, alertas regulatorias y recomendaciones de tratamiento fiscal.</t>
+  </si>
+  <si>
+    <t>Cumplimiento regulatorio automatizado; Interpretación de normas y regulación financiera; Identificación de inconsistencias en los registros de datos maestros</t>
   </si>
   <si>
     <t>¿Existe modelo operativo de impuestos indirectos?
@@ -461,10 +461,10 @@
     <t>Determinación integrada en ERP/facturación con controles preventivos, validación de maestros, excepciones y trazabilidad transaccional.</t>
   </si>
   <si>
-    <t>AI detecta tratamientos anómalos, incoherencias en maestros/códigos fiscales, errores de factura y recomienda correcciones antes de presentación.</t>
-  </si>
-  <si>
-    <t>Automated invoice error detection &amp; correction; Identify inconsistencies in master data records; Financial rules and regulations interpretations</t>
+    <t>IA detecta tratamientos anómalos, incoherencias en maestros/códigos fiscales, errores de factura y recomienda correcciones antes de presentación.</t>
+  </si>
+  <si>
+    <t>Detección y corrección automatizada de errores en facturas; Identificación de inconsistencias en los registros de datos maestros; Interpretación de normas y regulación financiera</t>
   </si>
   <si>
     <t>¿Las reglas fiscales están configuradas en sistemas?
@@ -497,10 +497,10 @@
     <t>Preparación integrada con datos transaccionales, validaciones automáticas, conciliación contable-fiscal y workflow de revisión/aprobación.</t>
   </si>
   <si>
-    <t>Generación asistida de declaraciones indirectas con AI, detección de transacciones anómalas, reconciliación inteligente y explicación de variaciones.</t>
-  </si>
-  <si>
-    <t>Automate tax filing processes, analyze financial data, and generate accurate tax reports; Accurate tax report generation; Reconcile account balances at transaction level</t>
+    <t>Generación asistida de declaraciones indirectas con IA, detección de transacciones anómalas, reconciliación inteligente y explicación de variaciones.</t>
+  </si>
+  <si>
+    <t>Automatización de la presentación de impuestos, análisis de datos financieros y generación precisa de informes fiscales; Generación precisa de informes fiscales; Conciliación de saldos contables a nivel de transacción</t>
   </si>
   <si>
     <t>¿Se concilian bases fiscales con contabilidad?
@@ -533,10 +533,10 @@
     <t>Gestión integrada de riesgos indirectos con KRIs, controles automatizados, change management, testing periódico y reporting a comités.</t>
   </si>
   <si>
-    <t>AI monitoriza cambios regulatorios, identifica transacciones de riesgo, recomienda actualizaciones de reglas y prioriza controles por exposición.</t>
-  </si>
-  <si>
-    <t>Monitor emerging regulations and evaluate current state compliance; Global policy tracking; Predictive compliance monitoring</t>
+    <t>IA monitoriza cambios regulatorios, identifica transacciones de riesgo, recomienda actualizaciones de reglas y prioriza controles por exposición.</t>
+  </si>
+  <si>
+    <t>Monitorización de la regulación emergente y evaluación del cumplimiento actual; Seguimiento de políticas globales; Monitorización predictiva del cumplimiento</t>
   </si>
   <si>
     <t>¿Se monitorizan cambios de IVA/impuestos indirectos?
@@ -572,10 +572,10 @@
     <t>Advisory integrado con negocio, operaciones, legal, finanzas y estrategia, con seguimiento de impacto, riesgos y decisiones.</t>
   </si>
   <si>
-    <t>Tax advisory AI-enabled con asistente de consultas, búsqueda normativa, recomendaciones preliminares y priorización de asuntos por riesgo/valor.</t>
-  </si>
-  <si>
-    <t>Evaluate tax laws and regulations and provide recommendations for tax planning, compliance, and risk management; Financial rules and regulations interpretations; Enterprise-wide data search and access</t>
+    <t>Tax advisory basado en IA con asistente de consultas, búsqueda normativa, recomendaciones preliminares y priorización de asuntos por riesgo/valor.</t>
+  </si>
+  <si>
+    <t>Evaluación de la normativa fiscal y emisión de recomendaciones de planificación fiscal, cumplimiento y gestión de riesgos; Interpretación de normas y regulación financiera; Búsqueda y acceso a datos en toda la compañía</t>
   </si>
   <si>
     <t>¿Existe proceso de intake y priorización de consultas?
@@ -608,10 +608,10 @@
     <t>Planificación integrada con estrategia, cash tax, estructura legal/operativa, transfer pricing, forecast y gobierno de riesgo fiscal.</t>
   </si>
   <si>
-    <t>Planificación predictiva AI-enabled que simula escenarios, impactos regulatorios, cash tax, riesgos y recomendaciones de optimización responsable.</t>
-  </si>
-  <si>
-    <t>Predictive tax planning, compliance, and risk management; Evaluate tax laws and regulations and provide recommendations; Generate investing strategies</t>
+    <t>Planificación predictiva basada en IA que simula escenarios, impactos regulatorios, cash tax, riesgos y recomendaciones de optimización responsable.</t>
+  </si>
+  <si>
+    <t>Planificación fiscal, cumplimiento y gestión de riesgos predictivos; Evaluación de la normativa fiscal y emisión de recomendaciones; Generación de estrategias de inversión</t>
   </si>
   <si>
     <t>¿Se realizan escenarios de planificación fiscal?
@@ -644,10 +644,10 @@
     <t>Riesgo fiscal integrado con ERM, provisión, controversias, cambios normativos, governance y seguimiento periódico de exposición.</t>
   </si>
   <si>
-    <t>AI detecta señales de riesgo fiscal, prioriza posiciones inciertas, simula exposición y recomienda mitigantes/documentación soporte.</t>
-  </si>
-  <si>
-    <t>Predictive tax planning, compliance, and risk management; AI-powered risk management and regulatory compliance; Predictive compliance monitoring</t>
+    <t>IA detecta señales de riesgo fiscal, prioriza posiciones inciertas, simula exposición y recomienda mitigantes/documentación soporte.</t>
+  </si>
+  <si>
+    <t>Planificación fiscal, cumplimiento y gestión de riesgos predictivos; Gestión de riesgos y cumplimiento regulatorio impulsados por IA; Monitorización predictiva del cumplimiento</t>
   </si>
   <si>
     <t>¿Existe inventario de riesgos fiscales?
@@ -680,10 +680,10 @@
     <t>Gestión de conocimiento integrada con workflow de consultas, actualización normativa, control de versiones, formación y reutilización de criterios.</t>
   </si>
   <si>
-    <t>Tax knowledge assistant AI-enabled que busca normativa, resume cambios, recupera precedentes y propone borradores de análisis o respuestas.</t>
-  </si>
-  <si>
-    <t>Financial rules and regulations interpretations; AI-powered archive access and extraction; Global policy tracking</t>
+    <t>Tax knowledge assistant basado en IA que busca normativa, resume cambios, recupera precedentes y propone borradores de análisis o respuestas.</t>
+  </si>
+  <si>
+    <t>Interpretación de normas y regulación financiera; Acceso y extracción documental impulsados por IA; Seguimiento de políticas globales</t>
   </si>
   <si>
     <t>¿Existe repositorio fiscal estructurado?

--- a/F3M_Fiscal_assessment_ready_AI_v0.xlsx
+++ b/F3M_Fiscal_assessment_ready_AI_v0.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="271">
   <si>
     <t>Capacidad</t>
   </si>
@@ -871,6 +871,54 @@
   </si>
   <si>
     <t>Evaluar situación actual, sustentar el score con evidencias, separar las tres palancas, validar resultados con responsables del dominio y preservar la conexión entre cumplimiento, riesgo, asesoramiento y valor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de informes fiscales; Preparación asistida de estados financieros; Análisis de desviaciones con explicación automática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de informes fiscales; Detección de inconsistencias en datos maestros; Análisis de desviaciones con explicación automática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integración automatizada de datos financieros; Detección de inconsistencias en datos maestros; Generación de documentación de metadatos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de informes fiscales; Consolidación de informes en un único documento; Análisis de desviaciones con explicación automática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatización de la presentación de impuestos; Cumplimiento regulatorio automatizado; Seguimiento de políticas y regulación global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatización de la presentación de impuestos; Generación de informes fiscales; Interpretación de normativa financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceso y extracción documental; Interpretación de normativa financiera; Informes de investigación y KYC; Respuesta asistida a requerimientos fiscales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitorización predictiva del cumplimiento; Cumplimiento regulatorio automatizado; Recomendaciones de resolución de incidencias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumplimiento regulatorio automatizado; Interpretación de normativa financiera; Detección de inconsistencias en datos maestros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección y corrección de errores en facturas; Detección de inconsistencias en datos maestros; Interpretación de normativa financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatización de la presentación de impuestos; Generación de informes fiscales; Conciliación a nivel de transacción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vigilancia de regulación emergente; Seguimiento de políticas y regulación global; Monitorización predictiva del cumplimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluación normativa y recomendación fiscal; Interpretación de normativa financiera; Consulta del dato en lenguaje natural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación fiscal predictiva; Evaluación normativa y recomendación fiscal; Generación de estrategias de inversión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación fiscal predictiva; Vigilancia continua de riesgo y cumplimiento; Monitorización predictiva del cumplimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretación de normativa financiera; Acceso y extracción documental; Seguimiento de políticas y regulación global</t>
   </si>
 </sst>
 </file>
@@ -1620,7 +1668,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>255</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1678,7 +1726,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>39</v>
+        <v>256</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1736,7 +1784,7 @@
         <v>49</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>257</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1794,7 +1842,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>61</v>
+        <v>258</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1852,7 +1900,7 @@
         <v>72</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1910,7 +1958,7 @@
         <v>83</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>84</v>
+        <v>260</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1968,7 +2016,7 @@
         <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>95</v>
+        <v>261</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -2026,7 +2074,7 @@
         <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>106</v>
+        <v>262</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2084,7 +2132,7 @@
         <v>117</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>118</v>
+        <v>263</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -2142,7 +2190,7 @@
         <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>129</v>
+        <v>264</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2200,7 +2248,7 @@
         <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>140</v>
+        <v>265</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2258,7 +2306,7 @@
         <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>151</v>
+        <v>266</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2316,7 +2364,7 @@
         <v>162</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>163</v>
+        <v>267</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2374,7 +2422,7 @@
         <v>173</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -2432,7 +2480,7 @@
         <v>184</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>185</v>
+        <v>269</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -2490,7 +2538,7 @@
         <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -3391,7 +3439,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>255</v>
       </c>
       <c r="G2" s="2" t="str">
         <f t="shared" ref="G2:G17" si="0">IF(C2="","",IF(C2&gt;=3,"Oleada 1",IF(C2=2,"Oleada 2",IF(C2=1,"Oleada 3",""))))</f>
@@ -3422,7 +3470,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>256</v>
       </c>
       <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3453,7 +3501,7 @@
         <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>257</v>
       </c>
       <c r="G4" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3484,7 +3532,7 @@
         <v>64</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>258</v>
       </c>
       <c r="G5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3515,7 +3563,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="G6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3546,7 +3594,7 @@
         <v>87</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>260</v>
       </c>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3577,7 +3625,7 @@
         <v>98</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>95</v>
+        <v>261</v>
       </c>
       <c r="G8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3608,7 +3656,7 @@
         <v>109</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>106</v>
+        <v>262</v>
       </c>
       <c r="G9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3639,7 +3687,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>118</v>
+        <v>263</v>
       </c>
       <c r="G10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3670,7 +3718,7 @@
         <v>132</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>129</v>
+        <v>264</v>
       </c>
       <c r="G11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3701,7 +3749,7 @@
         <v>143</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>140</v>
+        <v>265</v>
       </c>
       <c r="G12" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3732,7 +3780,7 @@
         <v>154</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>151</v>
+        <v>266</v>
       </c>
       <c r="G13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3763,7 +3811,7 @@
         <v>166</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>163</v>
+        <v>267</v>
       </c>
       <c r="G14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3794,7 +3842,7 @@
         <v>177</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="G15" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3825,7 +3873,7 @@
         <v>188</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>185</v>
+        <v>269</v>
       </c>
       <c r="G16" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3856,7 +3904,7 @@
         <v>199</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="G17" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3916,7 +3964,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>255</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -3933,7 +3981,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>256</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -3950,7 +3998,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>257</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>49</v>
@@ -3967,7 +4015,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>258</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>60</v>
@@ -3984,7 +4032,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>72</v>
@@ -4001,7 +4049,7 @@
         <v>77</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>260</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>83</v>
@@ -4018,7 +4066,7 @@
         <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>261</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>94</v>
@@ -4035,7 +4083,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>262</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>105</v>
@@ -4052,7 +4100,7 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>118</v>
+        <v>263</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>117</v>
@@ -4069,7 +4117,7 @@
         <v>122</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>129</v>
+        <v>264</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>128</v>
@@ -4086,7 +4134,7 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>140</v>
+        <v>265</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>139</v>
@@ -4103,7 +4151,7 @@
         <v>144</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>151</v>
+        <v>266</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>150</v>
@@ -4120,7 +4168,7 @@
         <v>156</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>163</v>
+        <v>267</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>162</v>
@@ -4137,7 +4185,7 @@
         <v>167</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>173</v>
@@ -4154,7 +4202,7 @@
         <v>178</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>185</v>
+        <v>269</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>184</v>
@@ -4171,7 +4219,7 @@
         <v>189</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>195</v>

--- a/F3M_Fiscal_assessment_ready_AI_v0.xlsx
+++ b/F3M_Fiscal_assessment_ready_AI_v0.xlsx
@@ -131,7 +131,7 @@
     <t>Proceso integrado con cierre, reporting, consolidación y fiscalidad local, con controles automatizados, trazabilidad y mejora continua.</t>
   </si>
   <si>
-    <t>Tax accounting continuo y basado en IA, con generación asistida de provisiones, validaciones inteligentes, alertas de desviación y explicación automática de variaciones.</t>
+    <t>Contabilidad fiscal continua y basada en IA, con generación asistida de provisiones, validaciones inteligentes, alertas de desviación y explicación automática de variaciones.</t>
   </si>
   <si>
     <t>Generación precisa de informes fiscales; Preparación automatizada de estados financieros; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
@@ -203,7 +203,7 @@
     <t>Capa integrada de datos fiscal-contables con controles automáticos, reconciliaciones recurrentes, gestión de incidencias y trazabilidad end-to-end.</t>
   </si>
   <si>
-    <t>IA detecta inconsistencias, clasificaciones anómalas y gaps de dato, genera metadata fiscal y recomienda acciones de remediación.</t>
+    <t>IA detecta inconsistencias, clasificaciones anómalas y lagunas de dato, genera metadatos fiscal y recomienda acciones de remediación.</t>
   </si>
   <si>
     <t>Automatización de datos financieros de fuentes diversas; Identificación de inconsistencias en los registros de datos maestros; Generación de documentación de metadatos</t>
@@ -239,7 +239,7 @@
     <t>Reporting integrado con cierre, forecast, auditoría, riesgos fiscales, acciones y revisión ejecutiva periódica.</t>
   </si>
   <si>
-    <t>Reporting fiscal basado en IA con generación automática de narrative commentary, explicación de variaciones, alertas y recomendaciones de gestión.</t>
+    <t>Informes fiscales basados en IA, con generación automática del comentario narrativo, explicación de las variaciones, alertas y recomendaciones de gestión.</t>
   </si>
   <si>
     <t>Generación precisa de informes fiscales; Consolidación de informes financieros en un único informe conforme a normativa; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
@@ -278,7 +278,7 @@
     <t>Cumplimiento integrado con datos financieros, workflow, gestión documental, alertas y reporting de estatus/riesgos.</t>
   </si>
   <si>
-    <t>Compliance directo basado en IA con monitorización de vencimientos, revisión asistida de obligaciones, alertas regulatorias y generación de borradores.</t>
+    <t>Cumplimiento directo basado en IA con monitorización de vencimientos, revisión asistida de obligaciones, alertas regulatorias y generación de borradores.</t>
   </si>
   <si>
     <t>Automatización de la presentación de impuestos, análisis de datos financieros y generación precisa de informes fiscales; Cumplimiento regulatorio automatizado; Seguimiento de políticas globales</t>
@@ -425,7 +425,7 @@
     <t>Modelo integrado con procesos comerciales, compras, ERP, facturación, maestros fiscales, controles automáticos y reporting de incidencias.</t>
   </si>
   <si>
-    <t>Modelo indirect tax basado en IA con monitorización continua de transacciones, detección de errores, alertas regulatorias y recomendaciones de tratamiento fiscal.</t>
+    <t>Modelo de impuestos indirectos basado en IA, con monitorización continua de las transacciones, detección de errores, alertas regulatorias y recomendación de tratamiento fiscal.</t>
   </si>
   <si>
     <t>Cumplimiento regulatorio automatizado; Interpretación de normas y regulación financiera; Identificación de inconsistencias en los registros de datos maestros</t>
@@ -497,7 +497,7 @@
     <t>Preparación integrada con datos transaccionales, validaciones automáticas, conciliación contable-fiscal y workflow de revisión/aprobación.</t>
   </si>
   <si>
-    <t>Generación asistida de declaraciones indirectas con IA, detección de transacciones anómalas, reconciliación inteligente y explicación de variaciones.</t>
+    <t>Generación asistida de declaraciones indirectas con IA, detección de transacciones anómalas, conciliación inteligente y explicación de variaciones.</t>
   </si>
   <si>
     <t>Automatización de la presentación de impuestos, análisis de datos financieros y generación precisa de informes fiscales; Generación precisa de informes fiscales; Conciliación de saldos contables a nivel de transacción</t>
@@ -572,7 +572,7 @@
     <t>Advisory integrado con negocio, operaciones, legal, finanzas y estrategia, con seguimiento de impacto, riesgos y decisiones.</t>
   </si>
   <si>
-    <t>Tax advisory basado en IA con asistente de consultas, búsqueda normativa, recomendaciones preliminares y priorización de asuntos por riesgo/valor.</t>
+    <t>Asesoría fiscal basada en IA, con asistente de consultas, búsqueda normativa, recomendaciones preliminares y priorización de asuntos por riesgo y valor.</t>
   </si>
   <si>
     <t>Evaluación de la normativa fiscal y emisión de recomendaciones de planificación fiscal, cumplimiento y gestión de riesgos; Interpretación de normas y regulación financiera; Búsqueda y acceso a datos en toda la compañía</t>
@@ -608,7 +608,7 @@
     <t>Planificación integrada con estrategia, cash tax, estructura legal/operativa, transfer pricing, forecast y gobierno de riesgo fiscal.</t>
   </si>
   <si>
-    <t>Planificación predictiva basada en IA que simula escenarios, impactos regulatorios, cash tax, riesgos y recomendaciones de optimización responsable.</t>
+    <t>Planificación predictiva basada en IA que simula escenarios, impactos regulatorios, impuesto pagado en caja, riesgos y recomendaciones de optimización responsable.</t>
   </si>
   <si>
     <t>Planificación fiscal, cumplimiento y gestión de riesgos predictivos; Evaluación de la normativa fiscal y emisión de recomendaciones; Generación de estrategias de inversión</t>
@@ -680,7 +680,7 @@
     <t>Gestión de conocimiento integrada con workflow de consultas, actualización normativa, control de versiones, formación y reutilización de criterios.</t>
   </si>
   <si>
-    <t>Tax knowledge assistant basado en IA que busca normativa, resume cambios, recupera precedentes y propone borradores de análisis o respuestas.</t>
+    <t>Asistente de conocimiento fiscal basado en IA, que busca la normativa, resume los cambios, recupera precedentes y propone borradores de análisis o de respuesta.</t>
   </si>
   <si>
     <t>Interpretación de normas y regulación financiera; Acceso y extracción documental impulsados por IA; Seguimiento de políticas globales</t>

--- a/F3M_Fiscal_assessment_ready_AI_v0.xlsx
+++ b/F3M_Fiscal_assessment_ready_AI_v0.xlsx
@@ -146,7 +146,7 @@
     <t>Calendario de cierre fiscal; RACI; workpapers de provisión; aprobaciones; conciliaciones; políticas contables/fiscales; evidencias de revisión.</t>
   </si>
   <si>
-    <t>Diseñar modelo de gobierno de tax accounting con calendario, RACI, controles, aprobaciones, trazabilidad de supuestos y conexión con cierre/reporting.</t>
+    <t>Diseñar modelo de gobierno de la contabilidad fiscal con calendario, RACI, controles, aprobaciones, trazabilidad de supuestos y conexión con cierre e informes.</t>
   </si>
   <si>
     <t>1.2 Cálculo de impuesto corriente, diferido y ETR</t>
@@ -182,7 +182,7 @@
     <t>Modelo de provisión; conciliación contable-fiscal; cálculo ETR; detalle de diferidos; ajustes permanentes/temporales; evidencias de revisión.</t>
   </si>
   <si>
-    <t>Estandarizar cálculo de impuesto corriente, diferido y ETR con reglas, conciliaciones, validaciones automáticas y análisis de drivers.</t>
+    <t>Estandarizar cálculo de impuesto corriente, diferido y tipo efectivo (ETR) con reglas, conciliaciones, validaciones automáticas y análisis de drivers.</t>
   </si>
   <si>
     <t>1.3 Calidad, integración y trazabilidad del dato fiscal-contable</t>
@@ -218,7 +218,7 @@
     <t>Modelo de datos fiscal; fuentes oficiales; reglas de calidad; reconciliaciones; incidencias de dato; documentación de ajustes; metadata.</t>
   </si>
   <si>
-    <t>Implantar capa de datos fiscal-contables con fuentes oficiales, reglas de calidad, reconciliaciones, owners y workflow de remediación.</t>
+    <t>Implantar capa de datos fiscal-contables con fuentes oficiales, reglas de calidad, conciliaciones, responsables y flujo de corrección.</t>
   </si>
   <si>
     <t>1.4 Reporting fiscal financiero y explicación ejecutiva</t>
@@ -254,7 +254,7 @@
     <t>Tax reporting pack; análisis ETR; cash tax; comentarios ejecutivos; actas de revisión; auditoría; acciones de seguimiento.</t>
   </si>
   <si>
-    <t>Crear reporting fiscal financiero con KPIs, narrativa ejecutiva, análisis de variaciones, riesgos, acciones y conexión con reporting externo.</t>
+    <t>Crear informes fiscales financieros con KPIs, narrativa ejecutiva, análisis de variaciones, riesgos, acciones y conexión con la información externa.</t>
   </si>
   <si>
     <t>Cumplimiento tributario directo</t>
@@ -293,7 +293,7 @@
     <t>Calendario fiscal; matriz de obligaciones; declaraciones; workflow de aprobación; evidencias; repositorio documental; alertas regulatorias.</t>
   </si>
   <si>
-    <t>Implantar gobierno de cumplimiento directo con calendario, matriz de obligaciones, workflow, repositorio de evidencias y alertas regulatorias.</t>
+    <t>Implantar gobierno de cumplimiento directo con calendario, matriz de obligaciones, flujo de trabajo, repositorio de evidencias y alertas regulatorias.</t>
   </si>
   <si>
     <t>2.2 Preparación, revisión y presentación de declaraciones directas</t>
@@ -329,7 +329,7 @@
     <t>Declaraciones directas; plantillas; fuentes de datos; logs de revisión; aprobaciones; documentación soporte; justificantes de presentación.</t>
   </si>
   <si>
-    <t>Estandarizar preparación y revisión de declaraciones directas con fuentes oficiales, validaciones, workflow y trazabilidad de ajustes.</t>
+    <t>Estandarizar preparación y revisión de declaraciones directas con fuentes oficiales, validaciones, flujo de trabajo y trazabilidad de ajustes.</t>
   </si>
   <si>
     <t>2.3 Controversias, requerimientos y relación con autoridades fiscales</t>
@@ -365,7 +365,7 @@
     <t>Tracker de controversias; requerimientos; respuestas; evidencias; actas con asesores; estimación de exposición; documentación de cierre.</t>
   </si>
   <si>
-    <t>Crear modelo de gestión de controversias fiscales con workflow, repositorio de evidencias, scoring de riesgo, reporting y lessons learned.</t>
+    <t>Crear modelo de gestión de controversias fiscales con flujo de trabajo, repositorio de evidencias, puntuación de riesgo, informes y lecciones aprendidas.</t>
   </si>
   <si>
     <t>2.4 Control, trazabilidad y mejora continua del cumplimiento directo</t>
@@ -440,7 +440,7 @@
     <t>Modelo operativo; calendario IVA; RACI; reglas fiscales; matriz de jurisdicciones; controles; incidencias; documentación de procesos.</t>
   </si>
   <si>
-    <t>Definir modelo operativo de impuestos indirectos con roles, calendario, reglas fiscales, controles, integración con procesos y reporting de incidencias.</t>
+    <t>Definir modelo operativo de impuestos indirectos con roles, calendario, reglas fiscales, controles, integración con procesos e informe de incidencias.</t>
   </si>
   <si>
     <t>3.2 Determinación fiscal en transacciones y facturación</t>
@@ -512,7 +512,7 @@
     <t>Declaraciones IVA; conciliaciones; libros registro; fuentes de datos; aprobaciones; ajustes; justificantes de presentación; reportes de errores.</t>
   </si>
   <si>
-    <t>Estandarizar preparación de declaraciones indirectas con conciliación contable-fiscal, validaciones automáticas, workflow y análisis de variaciones.</t>
+    <t>Estandarizar preparación de declaraciones indirectas con conciliación contable-fiscal, validaciones automáticas, flujo de trabajo y análisis de variaciones.</t>
   </si>
   <si>
     <t>3.4 Monitorización de riesgos, cambios regulatorios y controles indirectos</t>
@@ -548,7 +548,7 @@
     <t>Alertas regulatorias; análisis de impacto; cambios de configuración; matriz de controles; KRIs; incidencias; actas de seguimiento.</t>
   </si>
   <si>
-    <t>Crear modelo de monitorización de riesgos indirectos con regulatory tracking, análisis de impacto, KRIs, controles y actualización de reglas.</t>
+    <t>Crear modelo de monitorización de riesgos indirectos con seguimiento normativo, análisis de impacto, KRIs, controles y actualización de reglas.</t>
   </si>
   <si>
     <t>Asesoría fiscal</t>
@@ -587,7 +587,7 @@
     <t>Registro de consultas; tax memos; criterios de priorización; aprobaciones; actas con negocio; seguimiento de decisiones; feedback.</t>
   </si>
   <si>
-    <t>Definir modelo de tax advisory con intake, priorización por riesgo/valor, documentación estándar, approval workflow y seguimiento de impacto.</t>
+    <t>Definir modelo de asesoramiento fiscal con recepción de consultas, priorización por riesgo y valor, documentación estándar, flujo de aprobación y seguimiento de impacto.</t>
   </si>
   <si>
     <t>4.2 Planificación fiscal, escenarios y optimización dentro del marco normativo</t>
@@ -623,7 +623,7 @@
     <t>Tax planning memos; escenarios; cálculos de cash tax; análisis de sensibilidad; approvals; políticas de riesgo fiscal; business cases.</t>
   </si>
   <si>
-    <t>Crear framework de planificación fiscal con escenarios, cash tax, sensibilidad, riesgos, aprobaciones y conexión con forecast/estrategia.</t>
+    <t>Crear marco de planificación fiscal con escenarios, impuestos pagados en caja, sensibilidad, riesgos, aprobaciones y conexión con previsión y estrategia.</t>
   </si>
   <si>
     <t>4.3 Gestión de riesgos fiscales y posiciones inciertas</t>
@@ -659,7 +659,7 @@
     <t>Tax risk register; posiciones inciertas; cuantificación de exposición; mitigantes; actas de comité; provisiones; controversias.</t>
   </si>
   <si>
-    <t>Implantar tax risk register con clasificación, probabilidad/impacto, owners, mitigantes, conexión con provisión y reporting a governance.</t>
+    <t>Implantar registro de riesgos fiscales con clasificación, probabilidad e impacto, responsables, mitigantes, conexión con provisión e información a los órganos de gobierno.</t>
   </si>
   <si>
     <t>4.4 Gestión de conocimiento fiscal, normativa y soporte a decisiones</t>
@@ -695,7 +695,7 @@
     <t>Repositorio fiscal; tax memos; criterios técnicos; alertas normativas; plantillas; control de versiones; materiales de formación.</t>
   </si>
   <si>
-    <t>Crear tax knowledge hub con normativa, criterios, precedentes, templates, alertas de cambios y asistente de búsqueda/resumen.</t>
+    <t>Crear centro de conocimiento fiscal con normativa, criterios, precedentes, plantillas, alertas de cambios y asistente de búsqueda y resumen.</t>
   </si>
   <si>
     <t>Score global dominio</t>
